--- a/p3_data_preparation/data/spain/integrate_data/df_map_teams_fs_so.xlsx
+++ b/p3_data_preparation/data/spain/integrate_data/df_map_teams_fs_so.xlsx
@@ -493,10 +493,22 @@
           <t>rayo vallecano</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>480</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -512,10 +524,22 @@
           <t>las palmas</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>472</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -562,10 +586,22 @@
           <t>sevilla</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>481</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -600,10 +636,22 @@
           <t>getafe</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>1860</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -619,10 +667,22 @@
           <t>osasuna</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>479</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -638,10 +698,22 @@
           <t>mallorca</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>453</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -657,10 +729,22 @@
           <t>real sociedad</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>457</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -676,10 +760,22 @@
           <t>almeria</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>1861</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>almeria</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -695,10 +791,22 @@
           <t>betis</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>449</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>real betis</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -714,10 +822,22 @@
           <t>real madrid</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>243</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -733,10 +853,22 @@
           <t>alaves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>463</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>deportivo alaves</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -752,10 +884,22 @@
           <t>girona</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>110062</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -771,10 +915,22 @@
           <t>granada cf</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>110832</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>granada</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -790,10 +946,22 @@
           <t>cadiz cf</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>1968</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>cadiz</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -809,10 +977,22 @@
           <t>valencia</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>461</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>100</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -828,10 +1008,22 @@
           <t>barcelona</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>241</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>fc barcelona</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>100</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -847,10 +1039,22 @@
           <t>celta vigo</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>450</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>celta de vigo</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1804,10 +2008,22 @@
           <t>villarreal b</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>483</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>100</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
